--- a/data/DGS10_2010.xlsx
+++ b/data/DGS10_2010.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Real estate Forecast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3CE9F2-02BD-4E03-80E6-91129770CF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85B690B-E768-4413-9FD9-D8A618C103FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28710" yWindow="1095" windowWidth="22575" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daily" sheetId="2" r:id="rId1"/>
@@ -411,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B4261"/>
+  <dimension ref="A1:B4368"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" style="3" bestFit="1" customWidth="1"/>
@@ -33991,6 +33991,854 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
+    <row r="4262" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4262" s="3">
+        <v>46143</v>
+      </c>
+      <c r="B4262">
+        <v>4.3899999999999997</v>
+      </c>
+    </row>
+    <row r="4263" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4263" s="3">
+        <v>46146</v>
+      </c>
+      <c r="B4263">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="4264" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4264" s="3">
+        <v>46147</v>
+      </c>
+      <c r="B4264">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="4265" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4265" s="3">
+        <v>46148</v>
+      </c>
+      <c r="B4265">
+        <v>4.3600000000000003</v>
+      </c>
+    </row>
+    <row r="4266" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4266" s="3">
+        <v>46149</v>
+      </c>
+      <c r="B4266">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="4267" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4267" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B4267">
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="4268" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4268" s="3">
+        <v>46153</v>
+      </c>
+      <c r="B4268">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="4269" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4269" s="3">
+        <v>46154</v>
+      </c>
+      <c r="B4269">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="4270" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4270" s="3">
+        <v>46155</v>
+      </c>
+      <c r="B4270">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="4271" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4271" s="3">
+        <v>46156</v>
+      </c>
+      <c r="B4271">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="4272" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4272" s="3">
+        <v>46157</v>
+      </c>
+      <c r="B4272">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="4273" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4273" s="3">
+        <v>46160</v>
+      </c>
+      <c r="B4273">
+        <v>4.6100000000000003</v>
+      </c>
+    </row>
+    <row r="4274" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4274" s="3">
+        <v>46161</v>
+      </c>
+      <c r="B4274">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="4275" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4275" s="3">
+        <v>46162</v>
+      </c>
+      <c r="B4275">
+        <v>4.57</v>
+      </c>
+    </row>
+    <row r="4276" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4276" s="3">
+        <v>46163</v>
+      </c>
+      <c r="B4276">
+        <v>4.57</v>
+      </c>
+    </row>
+    <row r="4277" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4277" s="3">
+        <v>46164</v>
+      </c>
+      <c r="B4277">
+        <v>4.5599999999999996</v>
+      </c>
+    </row>
+    <row r="4278" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4278" s="3">
+        <v>46167</v>
+      </c>
+      <c r="B4278"/>
+    </row>
+    <row r="4279" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4279" s="3">
+        <v>46168</v>
+      </c>
+      <c r="B4279">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4280" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4280" s="3">
+        <v>46169</v>
+      </c>
+      <c r="B4280">
+        <v>4.4800000000000004</v>
+      </c>
+    </row>
+    <row r="4281" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4281" s="3">
+        <v>46170</v>
+      </c>
+      <c r="B4281">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="4282" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4282" s="3">
+        <v>46171</v>
+      </c>
+      <c r="B4282">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="4283" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4283" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B4283">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="4284" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4284" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B4284">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="4285" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4285" s="3">
+        <v>46176</v>
+      </c>
+      <c r="B4285">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="4286" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4286" s="3">
+        <v>46177</v>
+      </c>
+      <c r="B4286">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="4287" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4287" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B4287">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="4288" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4288" s="3">
+        <v>46181</v>
+      </c>
+      <c r="B4288">
+        <v>4.5599999999999996</v>
+      </c>
+    </row>
+    <row r="4289" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4289" s="3">
+        <v>46182</v>
+      </c>
+      <c r="B4289">
+        <v>4.53</v>
+      </c>
+    </row>
+    <row r="4290" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4290" s="3">
+        <v>46183</v>
+      </c>
+      <c r="B4290">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="4291" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4291" s="3">
+        <v>46184</v>
+      </c>
+      <c r="B4291">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="4292" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4292" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B4292">
+        <v>4.4800000000000004</v>
+      </c>
+    </row>
+    <row r="4293" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4293" s="3">
+        <v>46188</v>
+      </c>
+      <c r="B4293">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="4294" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4294" s="3">
+        <v>46189</v>
+      </c>
+      <c r="B4294">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="4295" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4295" s="3">
+        <v>46190</v>
+      </c>
+      <c r="B4295">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="4296" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4296" s="3">
+        <v>46191</v>
+      </c>
+      <c r="B4296">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="4297" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4297" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B4297"/>
+    </row>
+    <row r="4298" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4298" s="3">
+        <v>46195</v>
+      </c>
+      <c r="B4298">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="4299" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4299" s="3">
+        <v>46196</v>
+      </c>
+      <c r="B4299">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="4300" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4300" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B4300">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="4301" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4301" s="3">
+        <v>46198</v>
+      </c>
+      <c r="B4301">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="4302" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4302" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B4302">
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="4303" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4303" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B4303">
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="4304" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4304" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B4304">
+        <v>4.4400000000000004</v>
+      </c>
+    </row>
+    <row r="4305" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4305" s="3">
+        <v>46204</v>
+      </c>
+      <c r="B4305">
+        <v>4.4800000000000004</v>
+      </c>
+    </row>
+    <row r="4306" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4306" s="3">
+        <v>46205</v>
+      </c>
+      <c r="B4306">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="4307" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4307" s="3">
+        <v>46206</v>
+      </c>
+      <c r="B4307"/>
+    </row>
+    <row r="4308" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4308" s="3">
+        <v>46209</v>
+      </c>
+      <c r="B4308">
+        <v>4.4800000000000004</v>
+      </c>
+    </row>
+    <row r="4309" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4309" s="3">
+        <v>46210</v>
+      </c>
+      <c r="B4309">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="4310" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4310" s="3">
+        <v>46211</v>
+      </c>
+      <c r="B4310">
+        <v>4.5599999999999996</v>
+      </c>
+    </row>
+    <row r="4311" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4311" s="3">
+        <v>46212</v>
+      </c>
+      <c r="B4311">
+        <v>4.54</v>
+      </c>
+    </row>
+    <row r="4312" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4312" s="3">
+        <v>46213</v>
+      </c>
+      <c r="B4312">
+        <v>4.5599999999999996</v>
+      </c>
+    </row>
+    <row r="4313" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4313" s="3">
+        <v>46216</v>
+      </c>
+      <c r="B4313">
+        <v>4.62</v>
+      </c>
+    </row>
+    <row r="4314" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4314" s="3">
+        <v>46217</v>
+      </c>
+      <c r="B4314">
+        <v>4.58</v>
+      </c>
+    </row>
+    <row r="4315" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4315" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B4315">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="4316" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4316" s="3">
+        <v>46219</v>
+      </c>
+      <c r="B4316">
+        <v>4.57</v>
+      </c>
+    </row>
+    <row r="4317" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4317" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B4317">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="4318" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4318" s="3">
+        <v>46223</v>
+      </c>
+      <c r="B4318">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="4319" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4319" s="3">
+        <v>46224</v>
+      </c>
+      <c r="B4319">
+        <v>4.63</v>
+      </c>
+    </row>
+    <row r="4320" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4320" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B4320">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="4321" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4321" s="3">
+        <v>46226</v>
+      </c>
+      <c r="B4321">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="4322" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4322" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B4322">
+        <v>4.6900000000000004</v>
+      </c>
+    </row>
+    <row r="4323" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4323" s="3">
+        <v>46230</v>
+      </c>
+      <c r="B4323">
+        <v>4.6500000000000004</v>
+      </c>
+    </row>
+    <row r="4324" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4324" s="3">
+        <v>46231</v>
+      </c>
+      <c r="B4324">
+        <v>4.6100000000000003</v>
+      </c>
+    </row>
+    <row r="4325" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4325" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B4325">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="4326" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4326" s="3">
+        <v>46233</v>
+      </c>
+      <c r="B4326">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="4327" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4327" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B4327">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="4328" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4328" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B4328">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="4329" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4329" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B4329">
+        <v>4.63</v>
+      </c>
+    </row>
+    <row r="4330" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4330" s="3">
+        <v>46239</v>
+      </c>
+      <c r="B4330">
+        <v>4.63</v>
+      </c>
+    </row>
+    <row r="4331" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4331" s="3">
+        <v>46240</v>
+      </c>
+      <c r="B4331">
+        <v>4.6900000000000004</v>
+      </c>
+    </row>
+    <row r="4332" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4332" s="3">
+        <v>46241</v>
+      </c>
+      <c r="B4332">
+        <v>4.6500000000000004</v>
+      </c>
+    </row>
+    <row r="4333" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4333" s="3">
+        <v>46244</v>
+      </c>
+      <c r="B4333">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="4334" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4334" s="3">
+        <v>46245</v>
+      </c>
+      <c r="B4334">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="4335" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4335" s="3">
+        <v>46246</v>
+      </c>
+      <c r="B4335">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="4336" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4336" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B4336">
+        <v>4.63</v>
+      </c>
+    </row>
+    <row r="4337" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4337" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B4337">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="4338" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4338" s="3">
+        <v>46251</v>
+      </c>
+      <c r="B4338">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="4339" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4339" s="3">
+        <v>46252</v>
+      </c>
+      <c r="B4339">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="4340" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4340" s="3">
+        <v>46253</v>
+      </c>
+      <c r="B4340">
+        <v>4.6500000000000004</v>
+      </c>
+    </row>
+    <row r="4341" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4341" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B4341">
+        <v>4.6900000000000004</v>
+      </c>
+    </row>
+    <row r="4342" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4342" s="3">
+        <v>46255</v>
+      </c>
+      <c r="B4342">
+        <v>4.74</v>
+      </c>
+    </row>
+    <row r="4343" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4343" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B4343">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="4344" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4344" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B4344">
+        <v>4.6399999999999997</v>
+      </c>
+    </row>
+    <row r="4345" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4345" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B4345">
+        <v>4.66</v>
+      </c>
+    </row>
+    <row r="4346" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4346" s="3">
+        <v>46261</v>
+      </c>
+      <c r="B4346">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="4347" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4347" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B4347">
+        <v>4.7300000000000004</v>
+      </c>
+    </row>
+    <row r="4348" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4348" s="3">
+        <v>46265</v>
+      </c>
+      <c r="B4348">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="4349" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4349" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B4349">
+        <v>4.79</v>
+      </c>
+    </row>
+    <row r="4350" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4350" s="3">
+        <v>46267</v>
+      </c>
+      <c r="B4350">
+        <v>4.79</v>
+      </c>
+    </row>
+    <row r="4351" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4351" s="3">
+        <v>46268</v>
+      </c>
+      <c r="B4351">
+        <v>4.7699999999999996</v>
+      </c>
+    </row>
+    <row r="4352" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4352" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B4352">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="4353" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4353" s="3">
+        <v>46272</v>
+      </c>
+      <c r="B4353"/>
+    </row>
+    <row r="4354" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4354" s="3">
+        <v>46273</v>
+      </c>
+      <c r="B4354">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="4355" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4355" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B4355">
+        <v>4.83</v>
+      </c>
+    </row>
+    <row r="4356" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4356" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B4356">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="4357" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4357" s="3">
+        <v>46276</v>
+      </c>
+      <c r="B4357">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="4358" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4358" s="3">
+        <v>46279</v>
+      </c>
+      <c r="B4358">
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="4359" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4359" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B4359">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4360" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4360" s="3">
+        <v>46281</v>
+      </c>
+      <c r="B4360">
+        <v>5.01</v>
+      </c>
+    </row>
+    <row r="4361" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4361" s="3">
+        <v>46282</v>
+      </c>
+      <c r="B4361">
+        <v>4.9400000000000004</v>
+      </c>
+    </row>
+    <row r="4362" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4362" s="3">
+        <v>46283</v>
+      </c>
+      <c r="B4362">
+        <v>5.01</v>
+      </c>
+    </row>
+    <row r="4363" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4363" s="3">
+        <v>46286</v>
+      </c>
+      <c r="B4363">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="4364" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4364" s="3">
+        <v>46287</v>
+      </c>
+      <c r="B4364">
+        <v>4.96</v>
+      </c>
+    </row>
+    <row r="4365" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4365" s="3">
+        <v>46288</v>
+      </c>
+      <c r="B4365">
+        <v>5.1100000000000003</v>
+      </c>
+    </row>
+    <row r="4366" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4366" s="3">
+        <v>46289</v>
+      </c>
+      <c r="B4366">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="4367" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4367" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B4367">
+        <v>5.17</v>
+      </c>
+    </row>
+    <row r="4368" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4368" s="3">
+        <v>46293</v>
+      </c>
+      <c r="B4368">
+        <v>5.24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/DGS10_2010.xlsx
+++ b/data/DGS10_2010.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Real estate Forecast\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Real estate Forecast\RealEstateAI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85B690B-E768-4413-9FD9-D8A618C103FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188EC098-6DCA-4CA0-A6EC-BCB3B0BB2FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28710" yWindow="1095" windowWidth="22575" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25455" yWindow="3030" windowWidth="21600" windowHeight="12375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daily" sheetId="2" r:id="rId1"/>
@@ -411,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B4368"/>
+  <dimension ref="A1:B4370"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" style="3" bestFit="1" customWidth="1"/>
@@ -34839,6 +34839,22 @@
         <v>5.24</v>
       </c>
     </row>
+    <row r="4369" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4369" s="3">
+        <v>46294</v>
+      </c>
+      <c r="B4369" s="1">
+        <v>5.26</v>
+      </c>
+    </row>
+    <row r="4370" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4370" s="3">
+        <v>46295</v>
+      </c>
+      <c r="B4370" s="1">
+        <v>5.29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
